--- a/nail_artist_forms/004_nail_technician_client_consultation_form--nail_artist_forms.xlsx
+++ b/nail_artist_forms/004_nail_technician_client_consultation_form--nail_artist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nail_technician_client_consultation_form</t>
+          <t>client_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nail_client_consultation_form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Client's Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter client's name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,43 +542,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nail_client_preferences</t>
+          <t>nail_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nail_client_preferences</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Nail Type</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select nail type</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nail_type</t>
+          <t>nail_shape</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nail_type</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Nail Shape</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select nail shape</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nail_shape</t>
+          <t>nail_color</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nail_shape</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Nail Color</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select nail color</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nail_color</t>
+          <t>nail_length</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nail_color</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Nail Length</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter nail length</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nail_length</t>
+          <t>nail_width</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nail_length</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Nail Width</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter nail width</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nail_width</t>
+          <t>nail_thickening</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nail_width</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Nail Thickening</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select nail thickening</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nail_thickening</t>
+          <t>nail_strengthening</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nail_thickening</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Nail Strengthening</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select nail strengthening</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nail_strengthening</t>
+          <t>shape_strengthening</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nail_strengthening</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Shape Strengthening</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select nail shape strengthening</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nail_shape_strengthening</t>
+          <t>color_strengthening</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nail_shape_strengthening</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Color Strengthening</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select nail color strengthening</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nail_color_strengthening</t>
+          <t>client_contact</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nail_color_strengthening</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Client's Contact Information</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enter client's contact information</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,108 +817,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nail_shape_length</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nail_shape_length</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enter any additional comments</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>nail_shape_width</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>nail_shape_width</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>nail_length</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>nail_length</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>nail_width</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>nail_width</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>nail_thickening</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>nail_thickening</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -894,7 +850,7 @@
   <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1191,7 +1147,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>nail_strengthening_choices</t>
+          <t>nail_thickening_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1208,7 +1164,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>nail_strengthening_choices</t>
+          <t>nail_thickening_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1225,7 +1181,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nail_shape_strengthening_choices</t>
+          <t>nail_strengthening_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1242,7 +1198,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>nail_shape_strengthening_choices</t>
+          <t>nail_strengthening_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1259,7 +1215,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>nail_color_strengthening_choices</t>
+          <t>shape_strengthening_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1276,7 +1232,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>nail_color_strengthening_choices</t>
+          <t>shape_strengthening_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1293,7 +1249,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nail_thickening_choices</t>
+          <t>color_strengthening_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1310,7 +1266,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nail_thickening_choices</t>
+          <t>color_strengthening_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
